--- a/santhosh/Assets/3A_Catalog/Database files/JOB/DB_Jobs_List_Centra.xlsx
+++ b/santhosh/Assets/3A_Catalog/Database files/JOB/DB_Jobs_List_Centra.xlsx
@@ -972,13 +972,13 @@
     END;</t>
   </si>
   <si>
-    <t xml:space="preserve">select * from dba_jobs where SCHEMA_USER='HQOWCENTRA'</t>
-  </si>
-  <si>
     <t xml:space="preserve">job id</t>
   </si>
   <si>
-    <t xml:space="preserve">report</t>
+    <t xml:space="preserve">Report</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Status</t>
   </si>
   <si>
     <t xml:space="preserve">gl</t>
@@ -987,7 +987,7 @@
     <t xml:space="preserve">gl detail</t>
   </si>
   <si>
-    <t xml:space="preserve">b_partner his</t>
+    <t xml:space="preserve"> </t>
   </si>
   <si>
     <t xml:space="preserve">multiple</t>
@@ -1053,7 +1053,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="5">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -1081,18 +1081,19 @@
       <family val="0"/>
       <charset val="1"/>
     </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3465A4"/>
+        <bgColor rgb="FF3366FF"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -1146,7 +1147,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1159,6 +1160,66 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="FF000000"/>
+      <rgbColor rgb="FFFFFFFF"/>
+      <rgbColor rgb="FFFF0000"/>
+      <rgbColor rgb="FF00FF00"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008000"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FF808000"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FFC0C0C0"/>
+      <rgbColor rgb="FF808080"/>
+      <rgbColor rgb="FF9999FF"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FFFFFFCC"/>
+      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FF660066"/>
+      <rgbColor rgb="FFFF8080"/>
+      <rgbColor rgb="FF0066CC"/>
+      <rgbColor rgb="FFCCCCFF"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FF00CCFF"/>
+      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFCCFFCC"/>
+      <rgbColor rgb="FFFFFF99"/>
+      <rgbColor rgb="FF99CCFF"/>
+      <rgbColor rgb="FFFF99CC"/>
+      <rgbColor rgb="FFCC99FF"/>
+      <rgbColor rgb="FFFFCC99"/>
+      <rgbColor rgb="FF3366FF"/>
+      <rgbColor rgb="FF33CCCC"/>
+      <rgbColor rgb="FF99CC00"/>
+      <rgbColor rgb="FFFFCC00"/>
+      <rgbColor rgb="FFFF9900"/>
+      <rgbColor rgb="FFFF6600"/>
+      <rgbColor rgb="FF3465A4"/>
+      <rgbColor rgb="FF969696"/>
+      <rgbColor rgb="FF003366"/>
+      <rgbColor rgb="FF339966"/>
+      <rgbColor rgb="FF003300"/>
+      <rgbColor rgb="FF333300"/>
+      <rgbColor rgb="FF993300"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FF333399"/>
+      <rgbColor rgb="FF333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -1168,7 +1229,7 @@
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:R26"/>
-  <sheetFormatPr defaultColWidth="11.58984375" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.640625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5.73"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="14.62"/>
@@ -2511,168 +2572,166 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A2:D21"/>
-  <sheetFormatPr defaultColWidth="10.859375" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:E18"/>
+  <sheetFormatPr defaultColWidth="10.90234375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26.16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="82.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="82.69"/>
   </cols>
   <sheetData>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
+    <row r="1" s="4" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="4" t="s">
         <v>159</v>
       </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="B1" s="4" t="s">
         <v>160</v>
       </c>
+      <c r="E1" s="4" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="0" t="n">
+        <v>602</v>
+      </c>
+      <c r="B2" s="0" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="0" t="n">
+        <v>604</v>
+      </c>
+      <c r="B3" s="0" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="0" t="n">
+        <v>605</v>
+      </c>
       <c r="B4" s="0" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>164</v>
+      </c>
+      <c r="C4" s="0" t="s">
+        <v>165</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="n">
-        <v>602</v>
+        <v>610</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>167</v>
+      </c>
+      <c r="C5" s="0" t="s">
+        <v>165</v>
+      </c>
+      <c r="D5" s="0" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="n">
-        <v>604</v>
+        <v>611</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="n">
-        <v>605</v>
+        <v>613</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>164</v>
-      </c>
-      <c r="C7" s="0" t="s">
-        <v>165</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="n">
-        <v>610</v>
-      </c>
-      <c r="B8" s="0" t="s">
-        <v>167</v>
-      </c>
-      <c r="C8" s="0" t="s">
-        <v>165</v>
-      </c>
-      <c r="D8" s="0" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="n">
-        <v>611</v>
-      </c>
+        <v>614</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="0" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="n">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="n">
-        <v>614</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>616</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="0" t="n">
+        <v>617</v>
+      </c>
       <c r="B12" s="0" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="n">
-        <v>615</v>
+        <v>618</v>
       </c>
       <c r="B13" s="0" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="n">
-        <v>616</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>620</v>
+      </c>
+      <c r="B14" s="0" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="n">
-        <v>617</v>
+        <v>621</v>
       </c>
       <c r="B15" s="0" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="0" t="n">
-        <v>618</v>
+        <v>624</v>
       </c>
       <c r="B16" s="0" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="n">
-        <v>620</v>
+        <v>179</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="0" t="s">
+        <v>180</v>
       </c>
       <c r="B17" s="0" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="0" t="n">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="B18" s="0" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="n">
-        <v>624</v>
-      </c>
-      <c r="B19" s="0" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="s">
-        <v>180</v>
-      </c>
-      <c r="B20" s="0" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="0" t="n">
-        <v>622</v>
-      </c>
-      <c r="B21" s="0" t="s">
         <v>182</v>
       </c>
     </row>
